--- a/data/trans_bre/IP09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 15,45</t>
+          <t>-39,26; 15,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 51,93</t>
+          <t>-19,21; 52,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-81,47; -4,05</t>
+          <t>-82,01; -5,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 55,54</t>
+          <t>-7,31; 52,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 157,05</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,57</t>
+          <t>-100,0; 13,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 639,81</t>
+          <t>-22,44; 754,06</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,65; -8,5</t>
+          <t>-64,0; -8,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 37,62</t>
+          <t>-15,66; 42,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,63; 76,49</t>
+          <t>22,61; 75,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 33,65</t>
+          <t>-39,23; 31,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,24; 325,3</t>
+          <t>29,19; 315,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 411,83</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-53,02; -9,79</t>
+          <t>-51,62; -10,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 53,23</t>
+          <t>-1,53; 52,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 76,16</t>
+          <t>-28,33; 76,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 72,22</t>
+          <t>-42,27; 77,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 25,82</t>
+          <t>-16,91; 25,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 5,17</t>
+          <t>-33,06; 3,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 14,76</t>
+          <t>-41,19; 17,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 56,32</t>
+          <t>-12,38; 54,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 229,98</t>
+          <t>-56,01; 226,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,9; 12,77</t>
+          <t>-58,29; 13,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,2; 80,22</t>
+          <t>-73,54; 115,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,12; 470,3</t>
+          <t>-47,21; 554,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 25,27</t>
+          <t>-37,67; 20,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 36,03</t>
+          <t>-13,25; 38,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 58,49</t>
+          <t>-6,32; 56,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 35,03</t>
+          <t>-33,09; 38,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-85,45; 169,09</t>
+          <t>-100,0; 111,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 220,36</t>
+          <t>-33,09; 219,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 850,6</t>
+          <t>-20,41; 712,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 424,64</t>
+          <t>-68,2; 324,25</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 51,04</t>
+          <t>-40,2; 49,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 45,5</t>
+          <t>-52,48; 42,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,79; 26,61</t>
+          <t>-81,68; 26,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,61; 35,53</t>
+          <t>-59,25; 37,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,65; 241,13</t>
+          <t>-75,9; 264,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-80,32; 191,37</t>
+          <t>-77,87; 205,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,89</t>
+          <t>-100,0; 79,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 62,95</t>
+          <t>-75,82; 65,65</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 3,21</t>
+          <t>-21,37; 3,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 13,67</t>
+          <t>-8,86; 14,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 10,69</t>
+          <t>-24,45; 10,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 29,01</t>
+          <t>-4,51; 29,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 11,18</t>
+          <t>-61,58; 17,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 50,06</t>
+          <t>-25,25; 56,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 28,07</t>
+          <t>-45,9; 26,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 137,77</t>
+          <t>-14,27; 137,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Clase-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 15,04</t>
+          <t>-40,22; 10,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 52,58</t>
+          <t>-24,3; 53,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-82,01; -5,27</t>
+          <t>-82,9; -5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 52,68</t>
+          <t>-6,16; 55,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 157,05</t>
+          <t>-100,0; 137,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,25</t>
+          <t>-100,0; 8,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 754,06</t>
+          <t>-28,96; 715,11</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,0; -8,36</t>
+          <t>-64,83; -9,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 42,22</t>
+          <t>-17,63; 38,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,61; 75,91</t>
+          <t>21,71; 76,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 31,03</t>
+          <t>-41,16; 35,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 315,0</t>
+          <t>27,72; 329,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 411,83</t>
+          <t>-100,0; 470,6</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-51,62; -10,09</t>
+          <t>-50,07; -9,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 52,59</t>
+          <t>-2,98; 52,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 76,66</t>
+          <t>-25,43; 74,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 77,73</t>
+          <t>-37,4; 68,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 25,1</t>
+          <t>-18,53; 26,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 3,99</t>
+          <t>-30,29; 5,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 17,97</t>
+          <t>-43,33; 16,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 54,63</t>
+          <t>-14,31; 54,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 226,37</t>
+          <t>-57,48; 219,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 13,28</t>
+          <t>-55,11; 15,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,54; 115,6</t>
+          <t>-74,66; 102,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 554,0</t>
+          <t>-54,44; 412,07</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 20,04</t>
+          <t>-37,6; 25,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 38,37</t>
+          <t>-14,59; 37,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 56,63</t>
+          <t>-3,63; 61,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 38,11</t>
+          <t>-35,91; 37,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 111,62</t>
+          <t>-84,7; 173,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 219,67</t>
+          <t>-40,36; 201,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 712,28</t>
+          <t>-13,99; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-68,2; 324,25</t>
+          <t>-73,23; 264,51</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,2; 49,89</t>
+          <t>-40,59; 51,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,48; 42,24</t>
+          <t>-45,33; 46,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,68; 26,5</t>
+          <t>-81,58; 30,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,25; 37,03</t>
+          <t>-68,53; 36,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,9; 264,97</t>
+          <t>-79,68; 258,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,87; 205,73</t>
+          <t>-77,0; 234,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,2</t>
+          <t>-100,0; 96,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,82; 65,65</t>
+          <t>-75,82; 67,98</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 3,0</t>
+          <t>-21,61; 1,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 14,56</t>
+          <t>-9,79; 13,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 10,69</t>
+          <t>-23,07; 9,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 29,78</t>
+          <t>-5,54; 29,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 17,06</t>
+          <t>-61,01; 9,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 56,76</t>
+          <t>-26,27; 52,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 26,93</t>
+          <t>-40,81; 27,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 137,29</t>
+          <t>-16,68; 144,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,23</t>
+          <t>24,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>115,77%</t>
+          <t>107,75%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 10,5</t>
+          <t>-40,4; 15,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 53,45</t>
+          <t>-24,41; 51,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-82,9; -5,54</t>
+          <t>-81,47; -4,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 55,12</t>
+          <t>-6,55; 54,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,46</t>
+          <t>-100,0; 29,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 715,11</t>
+          <t>-30,02; 624,41</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,05</t>
+          <t>-6,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-12,52%</t>
+          <t>-20,03%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,83; -9,58</t>
+          <t>-64,65; -8,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 38,24</t>
+          <t>-13,7; 37,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,71; 76,71</t>
+          <t>22,63; 76,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 35,31</t>
+          <t>-44,78; 30,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,72; 329,39</t>
+          <t>29,24; 325,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 470,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>10,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-50,07; -9,73</t>
+          <t>-53,02; -9,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 52,57</t>
+          <t>-1,76; 53,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 74,05</t>
+          <t>-32,74; 76,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 68,74</t>
+          <t>-41,76; 70,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,53</t>
+          <t>-1,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>-5,73%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 26,29</t>
+          <t>-17,05; 25,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 5,75</t>
+          <t>-33,02; 5,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 16,2</t>
+          <t>-43,4; 14,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 54,56</t>
+          <t>-23,22; 20,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,48; 219,27</t>
+          <t>-54,08; 229,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 15,02</t>
+          <t>-58,9; 12,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,66; 102,6</t>
+          <t>-75,2; 80,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,44; 412,07</t>
+          <t>-69,97; 141,09</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-2,61%</t>
+          <t>-4,27%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 25,72</t>
+          <t>-37,91; 25,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 37,77</t>
+          <t>-15,02; 36,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 61,74</t>
+          <t>-6,35; 58,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 37,02</t>
+          <t>-30,73; 33,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,7; 173,28</t>
+          <t>-85,45; 169,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 201,15</t>
+          <t>-38,62; 220,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,99; —</t>
+          <t>-21,25; 850,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 264,51</t>
+          <t>-67,84; 360,38</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-9,47</t>
+          <t>-12,27</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-12,61%</t>
+          <t>-16,67%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 51,01</t>
+          <t>-43,41; 51,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 46,46</t>
+          <t>-50,21; 45,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,58; 30,39</t>
+          <t>-81,79; 26,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 36,98</t>
+          <t>-71,08; 34,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 258,82</t>
+          <t>-79,65; 241,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,0; 234,02</t>
+          <t>-80,32; 191,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,85</t>
+          <t>-100,0; 58,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,82; 67,98</t>
+          <t>-81,63; 63,11</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>2,66</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 1,8</t>
+          <t>-21,18; 3,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 13,77</t>
+          <t>-10,56; 13,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 9,76</t>
+          <t>-23,46; 10,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 29,31</t>
+          <t>-12,11; 16,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,01; 9,09</t>
+          <t>-61,31; 11,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 52,17</t>
+          <t>-28,24; 50,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 27,81</t>
+          <t>-43,24; 28,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 144,14</t>
+          <t>-32,2; 70,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,179 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-15,06</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13,54</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-51,33</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24,28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-52,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-79,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>107,75%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-15.06407707918261</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>13.54393475961776</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-51.33469724119522</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>24.27569437825398</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.5279188376162589</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.7303636865984242</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.7970415608981057</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.077469298402035</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-40,4; 15,45</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-24,41; 51,93</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-81,47; -4,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,55; 54,97</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 29,57</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-30,02; 624,41</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-40.39684056211551</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-24.4071421667932</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-81.46653477767654</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.54983611807319</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3002037154367183</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15.44826481305174</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>51.93315384657159</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-4.047886980624516</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>54.97240194898359</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="n">
+        <v>0.2956603525385512</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>6.244134236227223</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-33,06</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13,06</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46,42</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>145,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>86,65%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-20,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-64,65; -8,5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-13,7; 37,62</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22,63; 76,49</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-44,78; 30,14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,24; 325,3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-33.0614513787909</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>13.05932590140456</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>46.42374387673611</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-6.704165527859845</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.451632237785998</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.866498468462002</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.200323055600765</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-28,86</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19,35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>391,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-64.65406804470366</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-13.69513379155077</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>22.62936701920709</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-44.78367967599512</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="n">
+        <v>0.2924222166295691</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-53,02; -9,79</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,76; 53,23</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-32,74; 76,16</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-41,76; 70,88</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-8.503832578817297</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>37.62257838737692</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>76.49268844967403</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>30.1398618233635</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="n">
+        <v>3.252987510324043</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +799,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,77</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-13,51</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-13,37</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-28,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-33,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-5,73%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-28.86183248102844</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>19.34702349270654</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>31.16773371423616</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10.26853708736228</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>3.913889341564056</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.9196527194798561</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.365133732579402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-17,05; 25,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-33,02; 5,17</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-43,4; 14,76</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-23,22; 20,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-54,08; 229,98</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-58,9; 12,77</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-75,2; 80,22</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-69,97; 141,09</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-53.02050406373261</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.761711431935163</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-32.73951510821427</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-41.76260351690703</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-9.788076934792244</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>53.23256044667177</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>76.15559838663748</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>70.87568383636111</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-10,66</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-32,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,65%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>120,11%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-4,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-37,91; 25,27</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-15,02; 36,03</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,35; 58,49</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-30,73; 33,75</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-85,45; 169,09</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-38,62; 220,36</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-21,25; 850,6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-67,84; 360,38</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>4.773942162912734</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-13.50807812216038</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-13.37026443311773</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.475829295501552</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2041500037347531</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2819237511769197</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.3383100162986553</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.05729287108171064</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-43,61</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-12,27</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-1,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-61,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-16,67%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-17.05286711274342</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-33.02406725860473</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-43.40212143261195</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-23.22057999614335</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5408085476293978</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5890329850200277</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7519985424448615</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6996688226802713</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-43,41; 51,04</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-50,21; 45,5</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-81,79; 26,61</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-71,08; 34,27</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-79,65; 241,13</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-80,32; 191,37</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 58,89</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-81,63; 63,11</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>25.82399014073945</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.167776248305581</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>14.76341462211874</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>20.93053557497462</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.299790244318868</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1277478194273748</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.8022444264172448</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.410908352174843</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +983,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-9,91</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,18</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-33,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-13,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-10.65589747573768</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>11.00469927291679</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>29.17953521582393</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.201866790806522</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.3208295948323482</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.3765423968879245</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1.201115694645463</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.04267495277936075</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-21,18; 3,21</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-10,56; 13,67</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-23,46; 10,69</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-12,11; 16,65</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-61,31; 11,18</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-28,24; 50,06</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-43,24; 28,07</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-32,2; 70,16</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-37.90783409921556</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-15.02142710868415</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.354915563911378</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-30.73035694982483</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.854473325529442</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3862189140291082</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2124878927649508</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.6783841674598351</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>25.27059836340641</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>36.03383579090595</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>58.49386556214567</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>33.74872560841622</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.690895056195676</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.203619081248157</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>8.505969929856692</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>3.603842608494225</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>4.564248500163232</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-0.8885731006213149</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-43.60802157645179</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-12.26946299946314</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.112889293300601</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.01974948530128612</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.6145947002371938</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.1667036210845294</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-43.41480020066278</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-50.20639900561093</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-81.788282684934</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-71.08140625333587</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.7965276600449867</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8032345470426141</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.8162983273417533</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>51.04376819009878</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>45.49713319682227</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>26.61460853203775</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>34.2683008173374</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>2.411307103892908</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.913728315529505</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.588916133643733</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.6310654182360277</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-9.914721498430835</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.465098553914645</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-6.179893278121218</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>2.655472636401834</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.331029385458301</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.04540781651832608</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.1328912184211117</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.08810159048519606</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-21.18003936529369</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-10.56436967698016</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-23.46027641157002</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-12.11413522279905</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.6131133949072411</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2823941782277021</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.4324125012572386</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3219514322832959</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>3.20501123313967</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>13.66564580113845</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>10.68736880835813</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>16.65264854140123</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.1118430891585043</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.5006463696917264</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.2806504851643266</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.7016282549912906</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1281,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
